--- a/System_development/Pelican/structural_model/v0.3.0/BOM/BOM.xlsx
+++ b/System_development/Pelican/structural_model/v0.3.0/BOM/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/matthew_burnett_sc_edu/Documents/UAV/SWIFT-UAV/System_development/Pelican/structural_model/v0.3.0/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{00CFB75F-51B9-43AE-8AA6-13C529ACA0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B931A6E-3FDE-48D3-B69B-4BB16986A84A}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{00CFB75F-51B9-43AE-8AA6-13C529ACA0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{101B0AF9-66E2-4C05-8AC8-059640279637}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
   <si>
     <t>Name</t>
   </si>
@@ -307,9 +307,6 @@
     <t xml:space="preserve">Spare Required </t>
   </si>
   <si>
-    <t>KST DS215MG Servo</t>
-  </si>
-  <si>
     <t>Running Low</t>
   </si>
   <si>
@@ -326,6 +323,12 @@
   </si>
   <si>
     <t>Needed BOM omits parts the Iron bird will never need or parts that can readily be used for both, (video transmision for example)</t>
+  </si>
+  <si>
+    <t>DRONE CAN</t>
+  </si>
+  <si>
+    <t>KST DS215MG Servo (4pack)</t>
   </si>
 </sst>
 </file>
@@ -641,9 +644,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
@@ -654,6 +654,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -671,6 +674,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -970,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C3E270-438B-4BA7-BB0E-5AFFB906487D}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
@@ -982,16 +989,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
+      <c r="A1" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
     </row>
     <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51"/>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D3" s="1" t="s">
@@ -1018,20 +1025,20 @@
         <v>13</v>
       </c>
       <c r="E4" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" s="4">
         <v>1.6</v>
       </c>
       <c r="G4" s="4">
         <f>E4*F4</f>
-        <v>3.2</v>
+        <v>6.4</v>
       </c>
       <c r="H4" s="32" t="s">
         <v>11</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1045,7 +1052,7 @@
         <v>189</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" ref="G5:G16" si="0">E5*F5</f>
+        <f t="shared" ref="G5:G15" si="0">E5*F5</f>
         <v>189</v>
       </c>
       <c r="H5" s="32" t="s">
@@ -1094,217 +1101,200 @@
       <c r="I7" s="36"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D8" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="28">
-        <v>1</v>
-      </c>
-      <c r="F8" s="29">
-        <v>33.99</v>
-      </c>
-      <c r="G8" s="29">
-        <f t="shared" si="0"/>
-        <v>33.99</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="36"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D9" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
         <v>43.99</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G8" s="4">
         <f t="shared" si="0"/>
         <v>43.99</v>
       </c>
-      <c r="H9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="36"/>
+      <c r="H8" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="36"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D9" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="49">
+        <v>1</v>
+      </c>
+      <c r="F9" s="44">
+        <v>429.99</v>
+      </c>
+      <c r="G9" s="45">
+        <v>306</v>
+      </c>
+      <c r="H9" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D10" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="50">
-        <v>1</v>
-      </c>
-      <c r="F10" s="45">
-        <v>429.99</v>
-      </c>
-      <c r="G10" s="46">
-        <v>306</v>
-      </c>
-      <c r="H10" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="48" t="s">
-        <v>91</v>
+      <c r="D10" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="28">
+        <v>1</v>
+      </c>
+      <c r="F10" s="25">
+        <v>24.99</v>
+      </c>
+      <c r="G10" s="25">
+        <v>24.99</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D11" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="28">
-        <v>1</v>
-      </c>
-      <c r="F11" s="25">
-        <v>24.99</v>
-      </c>
-      <c r="G11" s="25">
-        <v>24.99</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D12" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4">
         <v>65</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G11" s="4">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
+      <c r="H11" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>280</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" ref="G12" si="1">E12*F12</f>
+        <v>280</v>
+      </c>
       <c r="H12" s="32" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="36"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4">
-        <v>280</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" ref="G13" si="1">E13*F13</f>
-        <v>280</v>
-      </c>
-      <c r="H13" s="32" t="s">
+      <c r="D13" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="28">
+        <v>1</v>
+      </c>
+      <c r="F13" s="29">
+        <v>156.02000000000001</v>
+      </c>
+      <c r="G13" s="29">
+        <f t="shared" si="0"/>
+        <v>156.02000000000001</v>
+      </c>
+      <c r="H13" s="34" t="s">
         <v>11</v>
       </c>
       <c r="I13" s="36"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D14" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="28">
-        <v>4</v>
-      </c>
-      <c r="F14" s="29">
-        <v>22.99</v>
-      </c>
-      <c r="G14" s="29">
+      <c r="D14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>175</v>
+      </c>
+      <c r="G14" s="4">
         <f t="shared" si="0"/>
-        <v>91.96</v>
-      </c>
-      <c r="H14" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="32" t="s">
         <v>11</v>
       </c>
       <c r="I14" s="36"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D15" s="5" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E15" s="3">
         <v>1</v>
       </c>
       <c r="F15" s="4">
-        <v>175</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>19.989999999999998</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="36"/>
+      <c r="I15" s="36" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D16" s="5" t="s">
-        <v>81</v>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E16" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16" s="4">
-        <v>19.989999999999998</v>
+        <v>12.57</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="0"/>
-        <v>19.989999999999998</v>
+        <f>E16*F16</f>
+        <v>62.85</v>
       </c>
       <c r="H16" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="36" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4">
-        <v>12.57</v>
-      </c>
-      <c r="G17" s="4">
-        <f>E17*F17</f>
-        <v>62.85</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="36"/>
-    </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D18" s="6" t="s">
+      <c r="I16" s="36"/>
+    </row>
+    <row r="17" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9">
-        <f>SUM(G4:G17)</f>
-        <v>1503.96</v>
-      </c>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D19" s="11"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9">
+        <f>SUM(G4:G16)</f>
+        <v>1537.2299999999998</v>
+      </c>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1313,18 +1303,17 @@
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" xr:uid="{A71CA281-0A96-4F2C-B0A0-7DE2B177E4E4}"/>
     <hyperlink ref="H7" r:id="rId2" xr:uid="{631C3AA5-0B9B-483E-A976-54A6F694ADD0}"/>
-    <hyperlink ref="H9" r:id="rId3" xr:uid="{4F621558-0637-4847-A464-18E614672C37}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{4F621558-0637-4847-A464-18E614672C37}"/>
     <hyperlink ref="H5" r:id="rId4" xr:uid="{B24F3DCD-FE50-4DF6-8818-079BF2668E20}"/>
-    <hyperlink ref="H12" r:id="rId5" xr:uid="{CB22CC0E-8246-402F-86D4-D20E93214A89}"/>
-    <hyperlink ref="H14" r:id="rId6" xr:uid="{D9C68F91-91B6-4560-BBCF-1DE3C7BC7E96}"/>
-    <hyperlink ref="H15" r:id="rId7" xr:uid="{061272B6-396D-427B-8C82-9FD009452DB6}"/>
-    <hyperlink ref="H17" r:id="rId8" xr:uid="{0AA494B9-98BE-48F1-9193-92445E693832}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{67F3049E-B6AE-4D68-AD78-5847EBE4CAD7}"/>
+    <hyperlink ref="H11" r:id="rId5" xr:uid="{CB22CC0E-8246-402F-86D4-D20E93214A89}"/>
+    <hyperlink ref="H13" r:id="rId6" xr:uid="{D9C68F91-91B6-4560-BBCF-1DE3C7BC7E96}"/>
+    <hyperlink ref="H14" r:id="rId7" xr:uid="{061272B6-396D-427B-8C82-9FD009452DB6}"/>
+    <hyperlink ref="H16" r:id="rId8" xr:uid="{0AA494B9-98BE-48F1-9193-92445E693832}"/>
+    <hyperlink ref="H9" r:id="rId9" xr:uid="{67F3049E-B6AE-4D68-AD78-5847EBE4CAD7}"/>
     <hyperlink ref="H6" r:id="rId10" xr:uid="{F1689D1E-249E-4954-BC71-74AFA59A2C5D}"/>
-    <hyperlink ref="H16" r:id="rId11" xr:uid="{44D9F2BA-6E50-4533-B62C-5863A713EC71}"/>
-    <hyperlink ref="H11" r:id="rId12" xr:uid="{A7609FF4-F633-490F-9878-05FA71BE6A10}"/>
-    <hyperlink ref="H8" r:id="rId13" xr:uid="{7FE20C2A-4E15-4934-B377-57B536835672}"/>
-    <hyperlink ref="H13" r:id="rId14" xr:uid="{8814B896-A013-471D-B330-AE21026F2406}"/>
+    <hyperlink ref="H15" r:id="rId11" xr:uid="{44D9F2BA-6E50-4533-B62C-5863A713EC71}"/>
+    <hyperlink ref="H10" r:id="rId12" xr:uid="{A7609FF4-F633-490F-9878-05FA71BE6A10}"/>
+    <hyperlink ref="H12" r:id="rId13" xr:uid="{8814B896-A013-471D-B330-AE21026F2406}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1455,7 +1444,7 @@
         <v>11</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
@@ -2201,20 +2190,20 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
@@ -2302,26 +2291,26 @@
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="44"/>
+      <c r="B28" s="51"/>
       <c r="C28">
         <f>10.7/20</f>
         <v>0.53499999999999992</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="44"/>
+      <c r="G28" s="51"/>
       <c r="H28">
         <f>11.675/20</f>
         <v>0.58374999999999999</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="K28" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="L28" s="44"/>
+      <c r="L28" s="51"/>
       <c r="M28">
         <f>13.3/20</f>
         <v>0.66500000000000004</v>
@@ -2379,26 +2368,26 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="44"/>
+      <c r="B32" s="51"/>
       <c r="C32">
         <f>12.4/20</f>
         <v>0.62</v>
       </c>
-      <c r="F32" s="44" t="s">
+      <c r="F32" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="G32" s="44"/>
+      <c r="G32" s="51"/>
       <c r="H32">
         <f>13.176/20</f>
         <v>0.65880000000000005</v>
       </c>
-      <c r="K32" s="44" t="s">
+      <c r="K32" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="L32" s="44"/>
+      <c r="L32" s="51"/>
       <c r="M32">
         <f>14.8/20</f>
         <v>0.74</v>
